--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 3.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 3.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14139CDE-DBFA-42AC-B04E-5791858B2E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
     <sheet name="Jawaban" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -163,7 +162,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -525,7 +524,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -610,9 +609,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -626,6 +622,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -685,10 +687,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -792,23 +794,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -844,23 +829,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1036,7 +1004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:P27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1060,19 +1028,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
     </row>
     <row r="2" spans="2:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="27" t="s">
@@ -1108,10 +1076,10 @@
       <c r="L2" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="44"/>
+      <c r="O2" s="45"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="19">
@@ -1123,18 +1091,36 @@
       <c r="D3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="19"/>
+      <c r="E3" s="19" t="str">
+        <f>VLOOKUP(D3,$N$3:$O$6,2,FALSE)</f>
+        <v>Toko Nofri</v>
+      </c>
       <c r="F3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="19" t="str">
+        <f>VLOOKUP(F3,$N$9:$P$13,2,FALSE)</f>
+        <v>Besi 5 Meter</v>
+      </c>
       <c r="H3" s="19">
         <v>340</v>
       </c>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="22"/>
+      <c r="I3" s="21">
+        <f>VLOOKUP(F3,$N$9:$P$13,3,FALSE)</f>
+        <v>200000</v>
+      </c>
+      <c r="J3" s="22">
+        <f>H3*I3</f>
+        <v>68000000</v>
+      </c>
+      <c r="K3" s="23">
+        <f>IF(H3&lt;200,0%,IF(H3&gt;500,20%,10%))</f>
+        <v>0.1</v>
+      </c>
+      <c r="L3" s="22">
+        <f>J3-(J3*K3)</f>
+        <v>61200000</v>
+      </c>
       <c r="N3" s="29" t="s">
         <v>14</v>
       </c>
@@ -1152,18 +1138,36 @@
       <c r="D4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="19"/>
+      <c r="E4" s="19" t="str">
+        <f t="shared" ref="E4:E17" si="0">VLOOKUP(D4,$N$3:$O$6,2,FALSE)</f>
+        <v>Toko Anton</v>
+      </c>
       <c r="F4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="19"/>
+      <c r="G4" s="19" t="str">
+        <f t="shared" ref="G4:G17" si="1">VLOOKUP(F4,$N$9:$P$13,2,FALSE)</f>
+        <v>Besi 10 Meter</v>
+      </c>
       <c r="H4" s="19">
         <v>140</v>
       </c>
-      <c r="I4" s="21"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="22"/>
+      <c r="I4" s="21">
+        <f t="shared" ref="I4:I17" si="2">VLOOKUP(F4,$N$9:$P$13,3,FALSE)</f>
+        <v>375000</v>
+      </c>
+      <c r="J4" s="22">
+        <f t="shared" ref="J4:J18" si="3">H4*I4</f>
+        <v>52500000</v>
+      </c>
+      <c r="K4" s="23">
+        <f t="shared" ref="K4:K17" si="4">IF(H4&lt;200,0%,IF(H4&gt;500,20%,10%))</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="22">
+        <f t="shared" ref="L4:L19" si="5">J4-(J4*K4)</f>
+        <v>52500000</v>
+      </c>
       <c r="N4" s="19" t="s">
         <v>12</v>
       </c>
@@ -1181,18 +1185,36 @@
       <c r="D5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="19"/>
+      <c r="E5" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Central</v>
+      </c>
       <c r="F5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="19"/>
+      <c r="G5" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pipa 5 Meter</v>
+      </c>
       <c r="H5" s="19">
         <v>560</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="22"/>
+      <c r="I5" s="21">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="J5" s="22">
+        <f t="shared" si="3"/>
+        <v>56000000</v>
+      </c>
+      <c r="K5" s="23">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="L5" s="22">
+        <f t="shared" si="5"/>
+        <v>44800000</v>
+      </c>
       <c r="N5" s="19" t="s">
         <v>16</v>
       </c>
@@ -1210,18 +1232,36 @@
       <c r="D6" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="19"/>
+      <c r="E6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Central</v>
+      </c>
       <c r="F6" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="19"/>
+      <c r="G6" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pipa 10 Meter</v>
+      </c>
       <c r="H6" s="19">
         <v>230</v>
       </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="22"/>
+      <c r="I6" s="21">
+        <f t="shared" si="2"/>
+        <v>185000</v>
+      </c>
+      <c r="J6" s="22">
+        <f t="shared" si="3"/>
+        <v>42550000</v>
+      </c>
+      <c r="K6" s="23">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="L6" s="22">
+        <f t="shared" si="5"/>
+        <v>38295000</v>
+      </c>
       <c r="N6" s="19" t="s">
         <v>13</v>
       </c>
@@ -1239,18 +1279,36 @@
       <c r="D7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="19"/>
+      <c r="E7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Anton</v>
+      </c>
       <c r="F7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="19"/>
+      <c r="G7" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Besi 5 Meter</v>
+      </c>
       <c r="H7" s="19">
         <v>770</v>
       </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="22"/>
+      <c r="I7" s="21">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+      <c r="J7" s="22">
+        <f t="shared" si="3"/>
+        <v>154000000</v>
+      </c>
+      <c r="K7" s="23">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="L7" s="22">
+        <f t="shared" si="5"/>
+        <v>123200000</v>
+      </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="19">
@@ -1262,23 +1320,41 @@
       <c r="D8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="19"/>
+      <c r="E8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Nofri</v>
+      </c>
       <c r="F8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="19"/>
+      <c r="G8" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Besi 10 Meter</v>
+      </c>
       <c r="H8" s="19">
         <v>780</v>
       </c>
-      <c r="I8" s="21"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="22"/>
-      <c r="N8" s="45" t="s">
+      <c r="I8" s="21">
+        <f t="shared" si="2"/>
+        <v>375000</v>
+      </c>
+      <c r="J8" s="22">
+        <f t="shared" si="3"/>
+        <v>292500000</v>
+      </c>
+      <c r="K8" s="23">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="L8" s="22">
+        <f t="shared" si="5"/>
+        <v>234000000</v>
+      </c>
+      <c r="N8" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="19">
@@ -1290,18 +1366,36 @@
       <c r="D9" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="19"/>
+      <c r="E9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Anton</v>
+      </c>
       <c r="F9" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="19"/>
+      <c r="G9" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pipa 5 Meter</v>
+      </c>
       <c r="H9" s="19">
         <v>300</v>
       </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="22"/>
+      <c r="I9" s="21">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="J9" s="22">
+        <f t="shared" si="3"/>
+        <v>30000000</v>
+      </c>
+      <c r="K9" s="23">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="L9" s="22">
+        <f t="shared" si="5"/>
+        <v>27000000</v>
+      </c>
       <c r="N9" s="29" t="s">
         <v>14</v>
       </c>
@@ -1322,18 +1416,36 @@
       <c r="D10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="19"/>
+      <c r="E10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Nofri</v>
+      </c>
       <c r="F10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="19"/>
+      <c r="G10" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pipa 10 Meter</v>
+      </c>
       <c r="H10" s="19">
         <v>790</v>
       </c>
-      <c r="I10" s="21"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="22"/>
+      <c r="I10" s="21">
+        <f t="shared" si="2"/>
+        <v>185000</v>
+      </c>
+      <c r="J10" s="22">
+        <f t="shared" si="3"/>
+        <v>146150000</v>
+      </c>
+      <c r="K10" s="23">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="L10" s="22">
+        <f t="shared" si="5"/>
+        <v>116920000</v>
+      </c>
       <c r="N10" s="19" t="s">
         <v>20</v>
       </c>
@@ -1354,18 +1466,36 @@
       <c r="D11" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="19"/>
+      <c r="E11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Central</v>
+      </c>
       <c r="F11" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="19"/>
+      <c r="G11" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Besi 5 Meter</v>
+      </c>
       <c r="H11" s="19">
         <v>440</v>
       </c>
-      <c r="I11" s="21"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="22"/>
+      <c r="I11" s="21">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+      <c r="J11" s="22">
+        <f t="shared" si="3"/>
+        <v>88000000</v>
+      </c>
+      <c r="K11" s="23">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="L11" s="22">
+        <f t="shared" si="5"/>
+        <v>79200000</v>
+      </c>
       <c r="N11" s="19" t="s">
         <v>21</v>
       </c>
@@ -1386,18 +1516,36 @@
       <c r="D12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="19"/>
+      <c r="E12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Anton</v>
+      </c>
       <c r="F12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="19"/>
+      <c r="G12" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Besi 10 Meter</v>
+      </c>
       <c r="H12" s="19">
         <v>130</v>
       </c>
-      <c r="I12" s="21"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="22"/>
+      <c r="I12" s="21">
+        <f t="shared" si="2"/>
+        <v>375000</v>
+      </c>
+      <c r="J12" s="22">
+        <f t="shared" si="3"/>
+        <v>48750000</v>
+      </c>
+      <c r="K12" s="23">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="22">
+        <f t="shared" si="5"/>
+        <v>48750000</v>
+      </c>
       <c r="N12" s="19" t="s">
         <v>22</v>
       </c>
@@ -1418,18 +1566,36 @@
       <c r="D13" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="19"/>
+      <c r="E13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Nofri</v>
+      </c>
       <c r="F13" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="19"/>
+      <c r="G13" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pipa 5 Meter</v>
+      </c>
       <c r="H13" s="19">
         <v>360</v>
       </c>
-      <c r="I13" s="21"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="22"/>
+      <c r="I13" s="21">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="J13" s="22">
+        <f t="shared" si="3"/>
+        <v>36000000</v>
+      </c>
+      <c r="K13" s="23">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="L13" s="22">
+        <f t="shared" si="5"/>
+        <v>32400000</v>
+      </c>
       <c r="N13" s="19" t="s">
         <v>23</v>
       </c>
@@ -1450,18 +1616,36 @@
       <c r="D14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="19"/>
+      <c r="E14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Nofri</v>
+      </c>
       <c r="F14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="19"/>
+      <c r="G14" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pipa 10 Meter</v>
+      </c>
       <c r="H14" s="19">
         <v>120</v>
       </c>
-      <c r="I14" s="21"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="22"/>
+      <c r="I14" s="21">
+        <f t="shared" si="2"/>
+        <v>185000</v>
+      </c>
+      <c r="J14" s="22">
+        <f t="shared" si="3"/>
+        <v>22200000</v>
+      </c>
+      <c r="K14" s="23">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="22">
+        <f t="shared" si="5"/>
+        <v>22200000</v>
+      </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="19">
@@ -1473,18 +1657,36 @@
       <c r="D15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="19"/>
+      <c r="E15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Anton</v>
+      </c>
       <c r="F15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="19"/>
+      <c r="G15" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pipa 5 Meter</v>
+      </c>
       <c r="H15" s="19">
         <v>120</v>
       </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="22"/>
+      <c r="I15" s="21">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="J15" s="22">
+        <f t="shared" si="3"/>
+        <v>12000000</v>
+      </c>
+      <c r="K15" s="23">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="22">
+        <f t="shared" si="5"/>
+        <v>12000000</v>
+      </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="19">
@@ -1496,18 +1698,36 @@
       <c r="D16" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="19"/>
+      <c r="E16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Nofri</v>
+      </c>
       <c r="F16" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="19"/>
+      <c r="G16" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pipa 10 Meter</v>
+      </c>
       <c r="H16" s="19">
         <v>720</v>
       </c>
-      <c r="I16" s="21"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="22"/>
+      <c r="I16" s="21">
+        <f t="shared" si="2"/>
+        <v>185000</v>
+      </c>
+      <c r="J16" s="22">
+        <f t="shared" si="3"/>
+        <v>133200000</v>
+      </c>
+      <c r="K16" s="23">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="L16" s="22">
+        <f t="shared" si="5"/>
+        <v>106560000</v>
+      </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="19">
@@ -1519,61 +1739,97 @@
       <c r="D17" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="19"/>
+      <c r="E17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Central</v>
+      </c>
       <c r="F17" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="19"/>
+      <c r="G17" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pipa 10 Meter</v>
+      </c>
       <c r="H17" s="19">
         <v>250</v>
       </c>
-      <c r="I17" s="21"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="22"/>
+      <c r="I17" s="21">
+        <f t="shared" si="2"/>
+        <v>185000</v>
+      </c>
+      <c r="J17" s="22">
+        <f t="shared" si="3"/>
+        <v>46250000</v>
+      </c>
+      <c r="K17" s="23">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="22">
+        <f t="shared" si="5"/>
+        <v>41625000</v>
+      </c>
     </row>
     <row r="18" spans="2:15" ht="1.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="36"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="39"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="38"/>
       <c r="H18" s="32"/>
       <c r="I18" s="33"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="34"/>
+      <c r="J18" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="34"/>
+      <c r="L18" s="22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="28">
+        <f>SUM(H3:H18)</f>
+        <v>6050</v>
+      </c>
+      <c r="I19" s="60"/>
+      <c r="J19" s="61"/>
       <c r="K19" s="30"/>
-      <c r="L19" s="31"/>
+      <c r="L19" s="31">
+        <f>SUM(L3:L18)</f>
+        <v>1040650000</v>
+      </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="25"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="25">
+        <f>AVERAGE(H3:H17)</f>
+        <v>403.33333333333331</v>
+      </c>
       <c r="I20" s="24"/>
       <c r="J20" s="24"/>
       <c r="K20" s="24"/>
-      <c r="L20" s="25"/>
+      <c r="L20" s="25">
+        <f>AVERAGE(L3:L17)</f>
+        <v>69376666.666666672</v>
+      </c>
     </row>
     <row r="21" spans="2:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
@@ -1639,13 +1895,13 @@
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
-      <c r="K26" s="60" t="s">
+      <c r="K26" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="L26" s="59"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="59"/>
-      <c r="O26" s="59"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="40"/>
     </row>
     <row r="27" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
@@ -1663,15 +1919,15 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B1:L1"/>
     <mergeCell ref="K26:O26"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="N8:P8"/>
-    <mergeCell ref="B1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K26" r:id="rId1" xr:uid="{3D800866-01AA-45F8-AF16-0A5339E31F09}"/>
+    <hyperlink ref="K26" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1679,7 +1935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1700,35 +1956,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="50"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="51"/>
       <c r="M1" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
       <c r="M2" s="5" t="s">
         <v>34</v>
       </c>
@@ -1767,10 +2023,10 @@
       <c r="K4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="54" t="s">
+      <c r="M4" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="54"/>
+      <c r="N4" s="55"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -2041,11 +2297,11 @@
         <f t="shared" si="5"/>
         <v>234000000</v>
       </c>
-      <c r="M10" s="54" t="s">
+      <c r="M10" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="N10" s="54"/>
-      <c r="O10" s="54"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="55"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -2462,14 +2718,14 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="57"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="58"/>
       <c r="G20" s="8">
         <f>SUM(G5:G19)</f>
         <v>6050</v>
@@ -2483,14 +2739,14 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="58" t="s">
+      <c r="A21" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
       <c r="G21" s="8">
         <f>G20/3</f>
         <v>2016.6666666666667</v>
@@ -2557,7 +2813,7 @@
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="M2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 3.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 3.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14139CDE-DBFA-42AC-B04E-5791858B2E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
     <sheet name="Jawaban" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -162,7 +163,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -524,7 +525,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -609,6 +610,9 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -622,12 +626,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -687,10 +685,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -794,6 +792,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -829,6 +844,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1004,7 +1036,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:P27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1028,19 +1060,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
     </row>
     <row r="2" spans="2:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="27" t="s">
@@ -1076,10 +1108,10 @@
       <c r="L2" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="45" t="s">
+      <c r="N2" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="45"/>
+      <c r="O2" s="44"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="19">
@@ -1091,36 +1123,18 @@
       <c r="D3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="19" t="str">
-        <f>VLOOKUP(D3,$N$3:$O$6,2,FALSE)</f>
-        <v>Toko Nofri</v>
-      </c>
+      <c r="E3" s="19"/>
       <c r="F3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="19" t="str">
-        <f>VLOOKUP(F3,$N$9:$P$13,2,FALSE)</f>
-        <v>Besi 5 Meter</v>
-      </c>
+      <c r="G3" s="19"/>
       <c r="H3" s="19">
         <v>340</v>
       </c>
-      <c r="I3" s="21">
-        <f>VLOOKUP(F3,$N$9:$P$13,3,FALSE)</f>
-        <v>200000</v>
-      </c>
-      <c r="J3" s="22">
-        <f>H3*I3</f>
-        <v>68000000</v>
-      </c>
-      <c r="K3" s="23">
-        <f>IF(H3&lt;200,0%,IF(H3&gt;500,20%,10%))</f>
-        <v>0.1</v>
-      </c>
-      <c r="L3" s="22">
-        <f>J3-(J3*K3)</f>
-        <v>61200000</v>
-      </c>
+      <c r="I3" s="21"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="22"/>
       <c r="N3" s="29" t="s">
         <v>14</v>
       </c>
@@ -1138,36 +1152,18 @@
       <c r="D4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="19" t="str">
-        <f t="shared" ref="E4:E17" si="0">VLOOKUP(D4,$N$3:$O$6,2,FALSE)</f>
-        <v>Toko Anton</v>
-      </c>
+      <c r="E4" s="19"/>
       <c r="F4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="19" t="str">
-        <f t="shared" ref="G4:G17" si="1">VLOOKUP(F4,$N$9:$P$13,2,FALSE)</f>
-        <v>Besi 10 Meter</v>
-      </c>
+      <c r="G4" s="19"/>
       <c r="H4" s="19">
         <v>140</v>
       </c>
-      <c r="I4" s="21">
-        <f t="shared" ref="I4:I17" si="2">VLOOKUP(F4,$N$9:$P$13,3,FALSE)</f>
-        <v>375000</v>
-      </c>
-      <c r="J4" s="22">
-        <f t="shared" ref="J4:J18" si="3">H4*I4</f>
-        <v>52500000</v>
-      </c>
-      <c r="K4" s="23">
-        <f t="shared" ref="K4:K17" si="4">IF(H4&lt;200,0%,IF(H4&gt;500,20%,10%))</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="22">
-        <f t="shared" ref="L4:L19" si="5">J4-(J4*K4)</f>
-        <v>52500000</v>
-      </c>
+      <c r="I4" s="21"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="22"/>
       <c r="N4" s="19" t="s">
         <v>12</v>
       </c>
@@ -1185,36 +1181,18 @@
       <c r="D5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Central</v>
-      </c>
+      <c r="E5" s="19"/>
       <c r="F5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Pipa 5 Meter</v>
-      </c>
+      <c r="G5" s="19"/>
       <c r="H5" s="19">
         <v>560</v>
       </c>
-      <c r="I5" s="21">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="J5" s="22">
-        <f t="shared" si="3"/>
-        <v>56000000</v>
-      </c>
-      <c r="K5" s="23">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
-      </c>
-      <c r="L5" s="22">
-        <f t="shared" si="5"/>
-        <v>44800000</v>
-      </c>
+      <c r="I5" s="21"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="22"/>
       <c r="N5" s="19" t="s">
         <v>16</v>
       </c>
@@ -1232,36 +1210,18 @@
       <c r="D6" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Central</v>
-      </c>
+      <c r="E6" s="19"/>
       <c r="F6" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Pipa 10 Meter</v>
-      </c>
+      <c r="G6" s="19"/>
       <c r="H6" s="19">
         <v>230</v>
       </c>
-      <c r="I6" s="21">
-        <f t="shared" si="2"/>
-        <v>185000</v>
-      </c>
-      <c r="J6" s="22">
-        <f t="shared" si="3"/>
-        <v>42550000</v>
-      </c>
-      <c r="K6" s="23">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="L6" s="22">
-        <f t="shared" si="5"/>
-        <v>38295000</v>
-      </c>
+      <c r="I6" s="21"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="22"/>
       <c r="N6" s="19" t="s">
         <v>13</v>
       </c>
@@ -1279,36 +1239,18 @@
       <c r="D7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Anton</v>
-      </c>
+      <c r="E7" s="19"/>
       <c r="F7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Besi 5 Meter</v>
-      </c>
+      <c r="G7" s="19"/>
       <c r="H7" s="19">
         <v>770</v>
       </c>
-      <c r="I7" s="21">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-      <c r="J7" s="22">
-        <f t="shared" si="3"/>
-        <v>154000000</v>
-      </c>
-      <c r="K7" s="23">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
-      </c>
-      <c r="L7" s="22">
-        <f t="shared" si="5"/>
-        <v>123200000</v>
-      </c>
+      <c r="I7" s="21"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="22"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="19">
@@ -1320,41 +1262,23 @@
       <c r="D8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Nofri</v>
-      </c>
+      <c r="E8" s="19"/>
       <c r="F8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Besi 10 Meter</v>
-      </c>
+      <c r="G8" s="19"/>
       <c r="H8" s="19">
         <v>780</v>
       </c>
-      <c r="I8" s="21">
-        <f t="shared" si="2"/>
-        <v>375000</v>
-      </c>
-      <c r="J8" s="22">
-        <f t="shared" si="3"/>
-        <v>292500000</v>
-      </c>
-      <c r="K8" s="23">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
-      </c>
-      <c r="L8" s="22">
-        <f t="shared" si="5"/>
-        <v>234000000</v>
-      </c>
-      <c r="N8" s="46" t="s">
+      <c r="I8" s="21"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="22"/>
+      <c r="N8" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="O8" s="46"/>
-      <c r="P8" s="46"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="45"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="19">
@@ -1366,36 +1290,18 @@
       <c r="D9" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Anton</v>
-      </c>
+      <c r="E9" s="19"/>
       <c r="F9" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Pipa 5 Meter</v>
-      </c>
+      <c r="G9" s="19"/>
       <c r="H9" s="19">
         <v>300</v>
       </c>
-      <c r="I9" s="21">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="J9" s="22">
-        <f t="shared" si="3"/>
-        <v>30000000</v>
-      </c>
-      <c r="K9" s="23">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="L9" s="22">
-        <f t="shared" si="5"/>
-        <v>27000000</v>
-      </c>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="22"/>
       <c r="N9" s="29" t="s">
         <v>14</v>
       </c>
@@ -1416,36 +1322,18 @@
       <c r="D10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Nofri</v>
-      </c>
+      <c r="E10" s="19"/>
       <c r="F10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Pipa 10 Meter</v>
-      </c>
+      <c r="G10" s="19"/>
       <c r="H10" s="19">
         <v>790</v>
       </c>
-      <c r="I10" s="21">
-        <f t="shared" si="2"/>
-        <v>185000</v>
-      </c>
-      <c r="J10" s="22">
-        <f t="shared" si="3"/>
-        <v>146150000</v>
-      </c>
-      <c r="K10" s="23">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
-      </c>
-      <c r="L10" s="22">
-        <f t="shared" si="5"/>
-        <v>116920000</v>
-      </c>
+      <c r="I10" s="21"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="22"/>
       <c r="N10" s="19" t="s">
         <v>20</v>
       </c>
@@ -1466,36 +1354,18 @@
       <c r="D11" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Central</v>
-      </c>
+      <c r="E11" s="19"/>
       <c r="F11" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Besi 5 Meter</v>
-      </c>
+      <c r="G11" s="19"/>
       <c r="H11" s="19">
         <v>440</v>
       </c>
-      <c r="I11" s="21">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-      <c r="J11" s="22">
-        <f t="shared" si="3"/>
-        <v>88000000</v>
-      </c>
-      <c r="K11" s="23">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="L11" s="22">
-        <f t="shared" si="5"/>
-        <v>79200000</v>
-      </c>
+      <c r="I11" s="21"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="22"/>
       <c r="N11" s="19" t="s">
         <v>21</v>
       </c>
@@ -1516,36 +1386,18 @@
       <c r="D12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Anton</v>
-      </c>
+      <c r="E12" s="19"/>
       <c r="F12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Besi 10 Meter</v>
-      </c>
+      <c r="G12" s="19"/>
       <c r="H12" s="19">
         <v>130</v>
       </c>
-      <c r="I12" s="21">
-        <f t="shared" si="2"/>
-        <v>375000</v>
-      </c>
-      <c r="J12" s="22">
-        <f t="shared" si="3"/>
-        <v>48750000</v>
-      </c>
-      <c r="K12" s="23">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="22">
-        <f t="shared" si="5"/>
-        <v>48750000</v>
-      </c>
+      <c r="I12" s="21"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="22"/>
       <c r="N12" s="19" t="s">
         <v>22</v>
       </c>
@@ -1566,36 +1418,18 @@
       <c r="D13" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Nofri</v>
-      </c>
+      <c r="E13" s="19"/>
       <c r="F13" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Pipa 5 Meter</v>
-      </c>
+      <c r="G13" s="19"/>
       <c r="H13" s="19">
         <v>360</v>
       </c>
-      <c r="I13" s="21">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="J13" s="22">
-        <f t="shared" si="3"/>
-        <v>36000000</v>
-      </c>
-      <c r="K13" s="23">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="L13" s="22">
-        <f t="shared" si="5"/>
-        <v>32400000</v>
-      </c>
+      <c r="I13" s="21"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="22"/>
       <c r="N13" s="19" t="s">
         <v>23</v>
       </c>
@@ -1616,36 +1450,18 @@
       <c r="D14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Nofri</v>
-      </c>
+      <c r="E14" s="19"/>
       <c r="F14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Pipa 10 Meter</v>
-      </c>
+      <c r="G14" s="19"/>
       <c r="H14" s="19">
         <v>120</v>
       </c>
-      <c r="I14" s="21">
-        <f t="shared" si="2"/>
-        <v>185000</v>
-      </c>
-      <c r="J14" s="22">
-        <f t="shared" si="3"/>
-        <v>22200000</v>
-      </c>
-      <c r="K14" s="23">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="22">
-        <f t="shared" si="5"/>
-        <v>22200000</v>
-      </c>
+      <c r="I14" s="21"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="19">
@@ -1657,36 +1473,18 @@
       <c r="D15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Anton</v>
-      </c>
+      <c r="E15" s="19"/>
       <c r="F15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Pipa 5 Meter</v>
-      </c>
+      <c r="G15" s="19"/>
       <c r="H15" s="19">
         <v>120</v>
       </c>
-      <c r="I15" s="21">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="J15" s="22">
-        <f t="shared" si="3"/>
-        <v>12000000</v>
-      </c>
-      <c r="K15" s="23">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="22">
-        <f t="shared" si="5"/>
-        <v>12000000</v>
-      </c>
+      <c r="I15" s="21"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="19">
@@ -1698,36 +1496,18 @@
       <c r="D16" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Nofri</v>
-      </c>
+      <c r="E16" s="19"/>
       <c r="F16" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Pipa 10 Meter</v>
-      </c>
+      <c r="G16" s="19"/>
       <c r="H16" s="19">
         <v>720</v>
       </c>
-      <c r="I16" s="21">
-        <f t="shared" si="2"/>
-        <v>185000</v>
-      </c>
-      <c r="J16" s="22">
-        <f t="shared" si="3"/>
-        <v>133200000</v>
-      </c>
-      <c r="K16" s="23">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
-      </c>
-      <c r="L16" s="22">
-        <f t="shared" si="5"/>
-        <v>106560000</v>
-      </c>
+      <c r="I16" s="21"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="19">
@@ -1739,97 +1519,61 @@
       <c r="D17" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Central</v>
-      </c>
+      <c r="E17" s="19"/>
       <c r="F17" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>Pipa 10 Meter</v>
-      </c>
+      <c r="G17" s="19"/>
       <c r="H17" s="19">
         <v>250</v>
       </c>
-      <c r="I17" s="21">
-        <f t="shared" si="2"/>
-        <v>185000</v>
-      </c>
-      <c r="J17" s="22">
-        <f t="shared" si="3"/>
-        <v>46250000</v>
-      </c>
-      <c r="K17" s="23">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="L17" s="22">
-        <f t="shared" si="5"/>
-        <v>41625000</v>
-      </c>
+      <c r="I17" s="21"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="2:15" ht="1.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="35"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="32"/>
       <c r="I18" s="33"/>
-      <c r="J18" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="34"/>
-      <c r="L18" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J18" s="34"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="34"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="28">
-        <f>SUM(H3:H18)</f>
-        <v>6050</v>
-      </c>
-      <c r="I19" s="60"/>
-      <c r="J19" s="61"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
       <c r="K19" s="30"/>
-      <c r="L19" s="31">
-        <f>SUM(L3:L18)</f>
-        <v>1040650000</v>
-      </c>
+      <c r="L19" s="31"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="25">
-        <f>AVERAGE(H3:H17)</f>
-        <v>403.33333333333331</v>
-      </c>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="25"/>
       <c r="I20" s="24"/>
       <c r="J20" s="24"/>
       <c r="K20" s="24"/>
-      <c r="L20" s="25">
-        <f>AVERAGE(L3:L17)</f>
-        <v>69376666.666666672</v>
-      </c>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="2:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
@@ -1895,13 +1639,13 @@
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
-      <c r="K26" s="39" t="s">
+      <c r="K26" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="40"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="59"/>
     </row>
     <row r="27" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
@@ -1919,15 +1663,15 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B1:L1"/>
     <mergeCell ref="K26:O26"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="N8:P8"/>
+    <mergeCell ref="B1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K26" r:id="rId1"/>
+    <hyperlink ref="K26" r:id="rId1" xr:uid="{3D800866-01AA-45F8-AF16-0A5339E31F09}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1935,7 +1679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1956,35 +1700,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="51"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="50"/>
       <c r="M1" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
       <c r="M2" s="5" t="s">
         <v>34</v>
       </c>
@@ -2023,10 +1767,10 @@
       <c r="K4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="55" t="s">
+      <c r="M4" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="55"/>
+      <c r="N4" s="54"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -2297,11 +2041,11 @@
         <f t="shared" si="5"/>
         <v>234000000</v>
       </c>
-      <c r="M10" s="55" t="s">
+      <c r="M10" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="N10" s="55"/>
-      <c r="O10" s="55"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -2718,14 +2462,14 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="58"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="57"/>
       <c r="G20" s="8">
         <f>SUM(G5:G19)</f>
         <v>6050</v>
@@ -2739,14 +2483,14 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
       <c r="G21" s="8">
         <f>G20/3</f>
         <v>2016.6666666666667</v>
@@ -2813,7 +2557,7 @@
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
